--- a/research/traditional_assets/database/data/peru/peru_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0316</v>
+        <v>-0.0214</v>
       </c>
       <c r="E2">
-        <v>-0.0008</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>274.2</v>
+        <v>201</v>
       </c>
       <c r="L2">
-        <v>0.3218687639394295</v>
+        <v>0.2628825529688726</v>
       </c>
       <c r="M2">
-        <v>154.8</v>
+        <v>109</v>
       </c>
       <c r="N2">
-        <v>0.06077022729949358</v>
+        <v>0.04324538781987701</v>
       </c>
       <c r="O2">
-        <v>0.5645514223194749</v>
+        <v>0.5422885572139303</v>
       </c>
       <c r="P2">
-        <v>154.8</v>
+        <v>109</v>
       </c>
       <c r="Q2">
-        <v>0.06077022729949358</v>
+        <v>0.04324538781987701</v>
       </c>
       <c r="R2">
-        <v>0.5645514223194749</v>
+        <v>0.5422885572139303</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>743.1</v>
+        <v>819.1</v>
       </c>
       <c r="V2">
-        <v>0.2917206453892356</v>
+        <v>0.3249752033326721</v>
       </c>
       <c r="W2">
-        <v>0.1637992831541218</v>
+        <v>0.1025144081195491</v>
       </c>
       <c r="X2">
-        <v>0.08019211067920749</v>
+        <v>0.08263814347045989</v>
       </c>
       <c r="Y2">
-        <v>0.08360717247491435</v>
+        <v>0.01987626464908925</v>
       </c>
       <c r="Z2">
-        <v>0.1722297474880213</v>
+        <v>0.1538492494667794</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06278145748936662</v>
+        <v>0.06583496068809667</v>
       </c>
       <c r="AC2">
-        <v>-0.06278145748936662</v>
+        <v>-0.06583496068809667</v>
       </c>
       <c r="AD2">
-        <v>3752.2</v>
+        <v>3384.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3752.2</v>
+        <v>3384.1</v>
       </c>
       <c r="AG2">
-        <v>3009.1</v>
+        <v>2565</v>
       </c>
       <c r="AH2">
-        <v>0.5956345741725534</v>
+        <v>0.5731294245164786</v>
       </c>
       <c r="AI2">
-        <v>0.6567942726111082</v>
+        <v>0.6080714426895226</v>
       </c>
       <c r="AJ2">
-        <v>0.5415556835361025</v>
+        <v>0.504375184347655</v>
       </c>
       <c r="AK2">
-        <v>0.6054770815726991</v>
+        <v>0.5404323458767014</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0316</v>
+        <v>-0.0214</v>
       </c>
       <c r="E3">
-        <v>-0.0008</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>274.2</v>
+        <v>201</v>
       </c>
       <c r="L3">
-        <v>0.3218687639394295</v>
+        <v>0.2628825529688726</v>
       </c>
       <c r="M3">
-        <v>154.8</v>
+        <v>109</v>
       </c>
       <c r="N3">
-        <v>0.06077022729949358</v>
+        <v>0.04324538781987701</v>
       </c>
       <c r="O3">
-        <v>0.5645514223194749</v>
+        <v>0.5422885572139303</v>
       </c>
       <c r="P3">
-        <v>154.8</v>
+        <v>109</v>
       </c>
       <c r="Q3">
-        <v>0.06077022729949358</v>
+        <v>0.04324538781987701</v>
       </c>
       <c r="R3">
-        <v>0.5645514223194749</v>
+        <v>0.5422885572139303</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>743.1</v>
+        <v>819.1</v>
       </c>
       <c r="V3">
-        <v>0.2917206453892356</v>
+        <v>0.3249752033326721</v>
       </c>
       <c r="W3">
-        <v>0.1637992831541218</v>
+        <v>0.1025144081195491</v>
       </c>
       <c r="X3">
-        <v>0.08019211067920749</v>
+        <v>0.08263814347045989</v>
       </c>
       <c r="Y3">
-        <v>0.08360717247491435</v>
+        <v>0.01987626464908925</v>
       </c>
       <c r="Z3">
-        <v>0.1722297474880213</v>
+        <v>0.1538492494667794</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06278145748936662</v>
+        <v>0.06583496068809667</v>
       </c>
       <c r="AC3">
-        <v>-0.06278145748936662</v>
+        <v>-0.06583496068809667</v>
       </c>
       <c r="AD3">
-        <v>3752.2</v>
+        <v>3384.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3752.2</v>
+        <v>3384.1</v>
       </c>
       <c r="AG3">
-        <v>3009.1</v>
+        <v>2565</v>
       </c>
       <c r="AH3">
-        <v>0.5956345741725534</v>
+        <v>0.5731294245164786</v>
       </c>
       <c r="AI3">
-        <v>0.6567942726111082</v>
+        <v>0.6080714426895226</v>
       </c>
       <c r="AJ3">
-        <v>0.5415556835361025</v>
+        <v>0.504375184347655</v>
       </c>
       <c r="AK3">
-        <v>0.6054770815726991</v>
+        <v>0.5404323458767014</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/peru/peru_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_banks_regional.xlsx
@@ -645,10 +645,10 @@
         <v>0.1025144081195491</v>
       </c>
       <c r="X2">
-        <v>0.08263814347045989</v>
+        <v>0.08262817649188561</v>
       </c>
       <c r="Y2">
-        <v>0.01987626464908925</v>
+        <v>0.01988623162766352</v>
       </c>
       <c r="Z2">
         <v>0.1538492494667794</v>
@@ -657,10 +657,10 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06583496068809667</v>
+        <v>0.06583070607821684</v>
       </c>
       <c r="AC2">
-        <v>-0.06583496068809667</v>
+        <v>-0.06583070607821684</v>
       </c>
       <c r="AD2">
         <v>3384.1</v>
@@ -767,10 +767,10 @@
         <v>0.1025144081195491</v>
       </c>
       <c r="X3">
-        <v>0.08263814347045989</v>
+        <v>0.08262817649188561</v>
       </c>
       <c r="Y3">
-        <v>0.01987626464908925</v>
+        <v>0.01988623162766352</v>
       </c>
       <c r="Z3">
         <v>0.1538492494667794</v>
@@ -779,10 +779,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06583496068809667</v>
+        <v>0.06583070607821684</v>
       </c>
       <c r="AC3">
-        <v>-0.06583496068809667</v>
+        <v>-0.06583070607821684</v>
       </c>
       <c r="AD3">
         <v>3384.1</v>
